--- a/data-manipulation-scripts/sheets-cleanup/sheets/ ESTATOR COMPLETO 09_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ ESTATOR COMPLETO 09_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -205,18 +205,6 @@
     <t>ESTATOR COMPLETO BHD JET50-C</t>
   </si>
   <si>
-    <t>7898508611209</t>
-  </si>
-  <si>
-    <t>ESTAROR BOBINA PULSO MAGNETRON CG125 FAN KS/ES 2009 A 2015 90278670</t>
-  </si>
-  <si>
-    <t>7898485614323</t>
-  </si>
-  <si>
-    <t>ESTAROR BOBINA PULSO MAGNETRON CG TITAN150 KS/ES/ESD 2004 A 2008</t>
-  </si>
-  <si>
     <t>7898932690016</t>
   </si>
   <si>
@@ -254,6 +242,9 @@
   </si>
   <si>
     <t>ESTATOR COMPLETO IRON BURMAN125I 2012 A 2018 350418</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>7895099120493</t>
@@ -299,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -314,6 +305,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,7 +565,9 @@
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>125.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -761,7 +757,9 @@
       <c r="C17" s="2">
         <v>1.0</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="2">
+        <v>265.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -785,7 +783,9 @@
       <c r="C19" s="2">
         <v>2.0</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="2">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
@@ -797,7 +797,9 @@
       <c r="C20" s="2">
         <v>3.0</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="2">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -821,7 +823,9 @@
       <c r="C22" s="2">
         <v>2.0</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
@@ -947,9 +951,7 @@
       <c r="C32" s="2">
         <v>1.0</v>
       </c>
-      <c r="D32" s="2">
-        <v>220.0</v>
-      </c>
+      <c r="D32" s="3"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
@@ -961,7 +963,9 @@
       <c r="C33" s="2">
         <v>1.0</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="2">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
@@ -971,45 +975,43 @@
         <v>69</v>
       </c>
       <c r="C34" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D34" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="D34" s="2">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="4"/>
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="C35" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D35" s="2">
-        <v>145.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="D35" s="3"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D36" s="3"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D36" s="2">
-        <v>145.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4"/>
       <c r="B37" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" s="3"/>
     </row>
@@ -1024,58 +1026,49 @@
         <v>1.0</v>
       </c>
       <c r="D38" s="3"/>
+      <c r="F38" s="5" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D39" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="D39" s="2">
+        <v>115.0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C40" s="2">
         <v>1.0</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="2">
+        <v>127.0</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D41" s="2">
-        <v>115.0</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>127.0</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43">
       <c r="A43" s="4"/>
@@ -6861,26 +6854,14 @@
       <c r="C1006" s="3"/>
       <c r="D1006" s="3"/>
     </row>
-    <row r="1007">
-      <c r="A1007" s="4"/>
-      <c r="B1007" s="3"/>
-      <c r="C1007" s="3"/>
-      <c r="D1007" s="3"/>
-    </row>
-    <row r="1008">
-      <c r="A1008" s="4"/>
-      <c r="B1008" s="3"/>
-      <c r="C1008" s="3"/>
-      <c r="D1008" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1008">
+  <conditionalFormatting sqref="A1:A1006">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1008">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1006">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
